--- a/sheets/대금율보/검수/여창 질음시조.xlsx
+++ b/sheets/대금율보/검수/여창 질음시조.xlsx
@@ -3854,8 +3854,7 @@
         <is>
           <t xml:space="preserve">–
 –
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="G5" s="22"/>
@@ -3987,8 +3986,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -4000,8 +3998,7 @@
         <is>
           <t xml:space="preserve">汰∧
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -4015,8 +4012,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K7" s="22"/>
@@ -4024,8 +4020,7 @@
         <is>
           <t xml:space="preserve">–
 –
-林И
-‹</t>
+林И</t>
         </is>
       </c>
       <c r="M7" s="22" t="inlineStr">
@@ -4039,8 +4034,7 @@
         <is>
           <t xml:space="preserve">–
 –
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="Q7" s="22"/>
@@ -4217,8 +4211,7 @@
         <is>
           <t xml:space="preserve">汰∧
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="E10" s="22"/>
@@ -4236,8 +4229,7 @@
         <is>
           <t xml:space="preserve">汰∧
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K10" s="22"/>
@@ -4245,8 +4237,7 @@
         <is>
           <t xml:space="preserve">–
 –
-И
-‹</t>
+И</t>
         </is>
       </c>
       <c r="M10" s="22" t="inlineStr">
@@ -4270,8 +4261,7 @@
         <is>
           <t xml:space="preserve">汰∧
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="Q10" s="22"/>
@@ -4355,8 +4345,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -4364,8 +4353,7 @@
         <is>
           <t xml:space="preserve">–
 –
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="G12" s="22"/>
@@ -4373,8 +4361,7 @@
         <is>
           <t xml:space="preserve">–
 –
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="I12" s="22"/>
@@ -4390,8 +4377,7 @@
         <is>
           <t xml:space="preserve">–
 –
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="M12" s="22"/>
@@ -4399,8 +4385,7 @@
         <is>
           <t xml:space="preserve">汰∧
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="O12" s="22"/>
@@ -4524,8 +4509,7 @@
         <is>
           <t xml:space="preserve">–
 –И
-潢
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="K14" s="22"/>
@@ -4592,8 +4576,7 @@
         <is>
           <t xml:space="preserve">林林フ
 –
-南)
-‹</t>
+南)</t>
         </is>
       </c>
       <c r="M15" s="22"/>

--- a/sheets/대금율보/검수/여창 질음시조.xlsx
+++ b/sheets/대금율보/검수/여창 질음시조.xlsx
@@ -3642,30 +3642,30 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="18.03" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="18.03" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="18.03" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="18.03" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="18.03" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="18.03" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="18.03" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="18.03" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="18.03" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="141.22" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="141.22" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="S4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="141.22" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="141.22" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
       </c>
       <c r="S6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="141.22" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="141.22" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="141.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -4203,7 +4203,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="141.22" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="22"/>
@@ -4268,7 +4268,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="141.22" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4337,7 +4337,7 @@
       <c r="R11" s="21"/>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="141.22" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -4394,7 +4394,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="141.22" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="22"/>
@@ -4477,7 +4477,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="141.22" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="22"/>
@@ -4528,7 +4528,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="141.22" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4609,6 +4609,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="67"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>